--- a/ESProvision/alarms.xlsx
+++ b/ESProvision/alarms.xlsx
@@ -5,15 +5,16 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/whuaning/Git/AutoOps/ESAlarmCreating/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/whuaning/Git/AutoOps/ESProvision/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DC1B2C98-B568-7E4B-801B-5059AD46843B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{272DB2FD-6B47-9745-99C5-8CCA9294473C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="800" yWindow="460" windowWidth="27620" windowHeight="17040" xr2:uid="{EFA5CA1F-2FCE-F944-B84C-F49CCED66540}"/>
+    <workbookView xWindow="840" yWindow="460" windowWidth="27620" windowHeight="17040" activeTab="1" xr2:uid="{EFA5CA1F-2FCE-F944-B84C-F49CCED66540}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="配置内容" sheetId="2" r:id="rId1"/>
+    <sheet name="告警清单" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -25,13 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="38">
-  <si>
-    <t>问题</t>
-  </si>
-  <si>
-    <t>如果使用量增加，群集可能会遇到内存不足错误。请考虑垂直扩展：Amazon ES 将实例的 RAM 的一半用于 Java 堆，最大堆大小为 32 GiB。您最多可以将实例的 RAM 垂直扩展至 64GiB，此时可以通过添加实例水平扩展。</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="77">
   <si>
     <t>考虑将更大的实例类型用于您的专用主节点。由于其在集群稳定性和蓝/绿部署中的作用，专用主节点的 CPU 使用率应比数据节点低。</t>
   </si>
@@ -117,9 +112,6 @@
     <t>您的集群中的节点已降至 20GiB 的可用存储空间。此值以 MiB 为单位，因此我们建议将其设置为每个节点的存储空间的 25%，而不是 20480。</t>
   </si>
   <si>
-    <t>您的群集正在阻止写入请求。</t>
-  </si>
-  <si>
     <t>自动快照失败。此故障通常由红色群集运行状况导致。</t>
   </si>
   <si>
@@ -139,13 +131,139 @@
   </si>
   <si>
     <t>&gt;1</t>
+  </si>
+  <si>
+    <t>服务</t>
+  </si>
+  <si>
+    <t>配置内容</t>
+  </si>
+  <si>
+    <t>上线事件</t>
+  </si>
+  <si>
+    <t>下线事件</t>
+  </si>
+  <si>
+    <t>EC2</t>
+  </si>
+  <si>
+    <t>实例启动</t>
+  </si>
+  <si>
+    <t>实例终止</t>
+  </si>
+  <si>
+    <t>RDS</t>
+  </si>
+  <si>
+    <t>实例删除</t>
+  </si>
+  <si>
+    <t>告警</t>
+  </si>
+  <si>
+    <t>AES</t>
+  </si>
+  <si>
+    <t>ELB</t>
+  </si>
+  <si>
+    <t>告警，标签，自动恢复</t>
+  </si>
+  <si>
+    <t>集群创建</t>
+  </si>
+  <si>
+    <t>实例创建</t>
+  </si>
+  <si>
+    <t>集群删除</t>
+  </si>
+  <si>
+    <t>AWS/EC2</t>
+  </si>
+  <si>
+    <t>问题描述</t>
+  </si>
+  <si>
+    <t>SystemStatusCheck</t>
+  </si>
+  <si>
+    <t>StatusCheckFailed_Instance</t>
+  </si>
+  <si>
+    <t>底层硬件故障，建议触发自动恢复</t>
+  </si>
+  <si>
+    <t>mem_used_percent</t>
+  </si>
+  <si>
+    <t>CWAgent</t>
+  </si>
+  <si>
+    <t>disk_used_percent</t>
+  </si>
+  <si>
+    <t>Linux文件系统空间不足</t>
+  </si>
+  <si>
+    <t>LogicalDisk % Free Space</t>
+  </si>
+  <si>
+    <t>&lt;=20</t>
+  </si>
+  <si>
+    <t>Windows文件系统空间不足</t>
+  </si>
+  <si>
+    <t>数据库RDS磁盘IO积分不足</t>
+  </si>
+  <si>
+    <t>AWS/RDS</t>
+  </si>
+  <si>
+    <t>UnHealthyHostCount</t>
+  </si>
+  <si>
+    <t>AWS/ApplicationELB</t>
+  </si>
+  <si>
+    <t>AWS/NetworkELB</t>
+  </si>
+  <si>
+    <t>BurstBalance</t>
+  </si>
+  <si>
+    <t>监控对象</t>
+  </si>
+  <si>
+    <t>EC2实例</t>
+  </si>
+  <si>
+    <t>ALB实例</t>
+  </si>
+  <si>
+    <t>RDS数据库实例</t>
+  </si>
+  <si>
+    <t>AES集群</t>
+  </si>
+  <si>
+    <t>您的集群正在阻止写入请求。</t>
+  </si>
+  <si>
+    <t>如果使用量增加，集群可能会遇到内存不足错误。请考虑垂直扩展：Amazon ES 将实例的 RAM 的一半用于 Java 堆，最大堆大小为 32 GiB。您最多可以将实例的 RAM 垂直扩展至 64GiB，此时可以通过添加实例水平扩展。</t>
+  </si>
+  <si>
+    <t>告警，标签，审计日志，慢查询日志</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -157,6 +275,12 @@
       <b/>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -187,13 +311,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -507,314 +631,658 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{157529DC-4008-E74A-89F0-DDFA0B3936F3}">
-  <dimension ref="A1:F15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55397CEC-137D-844F-972D-DFCD25C82959}">
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="89.6640625" customWidth="1"/>
+    <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{157529DC-4008-E74A-89F0-DDFA0B3936F3}">
+  <dimension ref="A1:G25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="51.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="G1" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2">
+        <v>300</v>
+      </c>
+      <c r="E2">
+        <v>3</v>
+      </c>
+      <c r="F2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D3">
+        <v>60</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D4">
+        <v>60</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
+      </c>
+      <c r="F4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D5">
+        <v>300</v>
+      </c>
+      <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="F5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D6">
+        <v>60</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>70</v>
+      </c>
+      <c r="B7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C7" t="s">
+        <v>60</v>
+      </c>
+      <c r="D7">
+        <v>60</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7" t="s">
+        <v>61</v>
+      </c>
+      <c r="G7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>71</v>
+      </c>
+      <c r="B8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C8" t="s">
+        <v>65</v>
+      </c>
+      <c r="D8">
+        <v>60</v>
+      </c>
+      <c r="E8">
+        <v>3</v>
+      </c>
+      <c r="F8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>71</v>
+      </c>
+      <c r="B9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D9">
+        <v>60</v>
+      </c>
+      <c r="E9">
+        <v>3</v>
+      </c>
+      <c r="F9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>72</v>
+      </c>
+      <c r="B10" t="s">
+        <v>64</v>
+      </c>
+      <c r="C10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10">
+        <v>300</v>
+      </c>
+      <c r="E10">
+        <v>3</v>
+      </c>
+      <c r="F10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>72</v>
+      </c>
+      <c r="B11" t="s">
+        <v>64</v>
+      </c>
+      <c r="C11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D11">
+        <v>60</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11" t="s">
+        <v>61</v>
+      </c>
+      <c r="G11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>73</v>
+      </c>
+      <c r="B12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="4" t="s">
+      <c r="D12">
+        <v>60</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12" t="s">
+        <v>8</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>73</v>
+      </c>
+      <c r="B13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13">
+        <v>60</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13" t="s">
+        <v>8</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>73</v>
+      </c>
+      <c r="B14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14">
+        <v>60</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14" t="s">
+        <v>11</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15">
+        <v>300</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15" t="s">
+        <v>8</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>73</v>
+      </c>
+      <c r="B16" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16">
+        <v>86400</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="F16" t="s">
+        <v>14</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>73</v>
+      </c>
+      <c r="B17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17">
+        <v>60</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="F17" t="s">
+        <v>8</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>73</v>
+      </c>
+      <c r="B18" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" t="s">
+        <v>16</v>
+      </c>
+      <c r="D18">
+        <v>300</v>
+      </c>
+      <c r="E18">
+        <v>3</v>
+      </c>
+      <c r="F18" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>73</v>
+      </c>
+      <c r="B19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" t="s">
+        <v>17</v>
+      </c>
+      <c r="D19">
+        <v>300</v>
+      </c>
+      <c r="E19">
+        <v>3</v>
+      </c>
+      <c r="F19" t="s">
+        <v>18</v>
+      </c>
+      <c r="G19" s="4"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>73</v>
+      </c>
+      <c r="B20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20">
+        <v>300</v>
+      </c>
+      <c r="E20">
+        <v>3</v>
+      </c>
+      <c r="F20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>73</v>
+      </c>
+      <c r="B21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" t="s">
+        <v>20</v>
+      </c>
+      <c r="D21">
+        <v>300</v>
+      </c>
+      <c r="E21">
+        <v>3</v>
+      </c>
+      <c r="F21" t="s">
+        <v>18</v>
+      </c>
+      <c r="G21" s="4"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>73</v>
+      </c>
+      <c r="B22" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" t="s">
+        <v>21</v>
+      </c>
+      <c r="D22">
+        <v>300</v>
+      </c>
+      <c r="E22">
+        <v>3</v>
+      </c>
+      <c r="F22" t="s">
+        <v>22</v>
+      </c>
+      <c r="G22" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>73</v>
+      </c>
+      <c r="B23" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" t="s">
+        <v>33</v>
+      </c>
+      <c r="D23">
+        <v>300</v>
+      </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
+      <c r="F23" t="s">
+        <v>18</v>
+      </c>
+      <c r="G23" s="3"/>
+    </row>
+    <row r="24" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>73</v>
+      </c>
+      <c r="B24" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" t="s">
+        <v>23</v>
+      </c>
+      <c r="D24">
+        <v>60</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+      <c r="F24" t="s">
         <v>8</v>
       </c>
-      <c r="C2">
-        <v>60</v>
-      </c>
-      <c r="D2">
+      <c r="G24" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>73</v>
+      </c>
+      <c r="B25" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" t="s">
+        <v>24</v>
+      </c>
+      <c r="D25">
+        <v>60</v>
+      </c>
+      <c r="E25">
         <v>1</v>
       </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3">
-        <v>60</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4">
-        <v>60</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5">
-        <v>300</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6">
-        <v>86400</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7">
-        <v>60</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" s="1" t="s">
+      <c r="F25" t="s">
+        <v>34</v>
+      </c>
+      <c r="G25" s="1" t="s">
         <v>31</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8">
-        <v>300</v>
-      </c>
-      <c r="D8">
-        <v>3</v>
-      </c>
-      <c r="E8" t="s">
-        <v>20</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9">
-        <v>300</v>
-      </c>
-      <c r="D9">
-        <v>3</v>
-      </c>
-      <c r="E9" t="s">
-        <v>20</v>
-      </c>
-      <c r="F9" s="3"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10">
-        <v>300</v>
-      </c>
-      <c r="D10">
-        <v>3</v>
-      </c>
-      <c r="E10" t="s">
-        <v>20</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11">
-        <v>300</v>
-      </c>
-      <c r="D11">
-        <v>3</v>
-      </c>
-      <c r="E11" t="s">
-        <v>20</v>
-      </c>
-      <c r="F11" s="3"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12">
-        <v>300</v>
-      </c>
-      <c r="D12">
-        <v>3</v>
-      </c>
-      <c r="E12" t="s">
-        <v>24</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" t="s">
-        <v>36</v>
-      </c>
-      <c r="C13">
-        <v>300</v>
-      </c>
-      <c r="D13">
-        <v>1</v>
-      </c>
-      <c r="E13" t="s">
-        <v>20</v>
-      </c>
-      <c r="F13" s="2"/>
-    </row>
-    <row r="14" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>9</v>
-      </c>
-      <c r="B14" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14">
-        <v>60</v>
-      </c>
-      <c r="D14">
-        <v>1</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>9</v>
-      </c>
-      <c r="B15" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15">
-        <v>60</v>
-      </c>
-      <c r="D15">
-        <v>1</v>
-      </c>
-      <c r="E15" t="s">
-        <v>37</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>34</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="G20:G21"/>
+    <mergeCell ref="G18:G19"/>
   </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>